--- a/Data/FlightPlan/FPL_07AUG26.xlsx
+++ b/Data/FlightPlan/FPL_07AUG26.xlsx
@@ -500,36 +500,36 @@
     <t>VN-A536</t>
   </si>
   <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A537</t>
+  </si>
+  <si>
     <t>07:50</t>
   </si>
   <si>
     <t>09:45</t>
   </si>
   <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A537</t>
-  </si>
-  <si>
     <t>13:35</t>
   </si>
   <si>
@@ -1019,6 +1019,9 @@
     <t>VN-A651</t>
   </si>
   <si>
+    <t>07:25</t>
+  </si>
+  <si>
     <t>KUL</t>
   </si>
   <si>
@@ -1169,9 +1172,6 @@
     <t>VN-A684</t>
   </si>
   <si>
-    <t>07:25</t>
-  </si>
-  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1271,7 +1271,7 @@
     <t>Total Record(s): 442</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 07, 2026 02:06</t>
+    <t xml:space="preserve">Generated on  Aug 07, 2026 03:41</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4416,7 +4416,7 @@
         <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>531</v>
+        <v>425</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
@@ -4432,13 +4432,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4449,7 +4449,7 @@
         <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>532</v>
+        <v>426</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
@@ -4462,16 +4462,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4482,7 +4482,7 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>425</v>
+        <v>147</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
@@ -4498,13 +4498,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c t="s" r="A97" s="6">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B97" s="7">
-        <v>426</v>
+        <v>828</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
@@ -4528,79 +4528,61 @@
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c t="s" r="A98" s="6">
-        <v>13</v>
-      </c>
-      <c r="B98" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="C98" s="7">
-        <v>14</v>
-      </c>
+      <c r="A98" s="6"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
       <c r="D98" s="7"/>
-      <c t="s" r="E98" s="7">
-        <v>162</v>
-      </c>
-      <c r="F98" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G98" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H98" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I98" s="7">
-        <v>168</v>
-      </c>
-      <c t="s" r="J98" s="7">
-        <v>169</v>
-      </c>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c t="s" r="A99" s="6">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>828</v>
+        <v>531</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>171</v>
@@ -4610,16 +4592,34 @@
       <c r="M99" s="7"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
+      <c t="s" r="A100" s="6">
+        <v>13</v>
+      </c>
+      <c r="B100" s="7">
+        <v>532</v>
+      </c>
+      <c t="s" r="C100" s="7">
+        <v>14</v>
+      </c>
       <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="7"/>
+      <c t="s" r="E100" s="7">
+        <v>170</v>
+      </c>
+      <c r="F100" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G100" s="8">
+        <v>39</v>
+      </c>
+      <c t="s" r="H100" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I100" s="7">
+        <v>89</v>
+      </c>
+      <c t="s" r="J100" s="7">
+        <v>172</v>
+      </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4831,7 +4831,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4864,7 +4864,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5107,7 +5107,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>188</v>
@@ -5206,7 +5206,7 @@
         <v>189</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>190</v>
@@ -5839,13 +5839,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5869,7 +5869,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>17</v>
@@ -7127,7 +7127,7 @@
         <v>251</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7359,7 +7359,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7507,7 +7507,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>63</v>
@@ -7831,7 +7831,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>229</v>
@@ -7861,7 +7861,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>20</v>
@@ -8230,7 +8230,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8323,7 +8323,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>108</v>
@@ -8353,7 +8353,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>17</v>
@@ -8572,7 +8572,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>267</v>
@@ -9277,7 +9277,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>296</v>
@@ -9850,7 +9850,7 @@
         <v>263</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>70</v>
@@ -10309,7 +10309,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>158</v>
@@ -10558,7 +10558,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10636,7 +10636,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>42</v>
@@ -11256,7 +11256,7 @@
         <v>13</v>
       </c>
       <c r="B320" s="7">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
@@ -11272,13 +11272,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>112</v>
+        <v>304</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11289,7 +11289,7 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
@@ -11302,16 +11302,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>187</v>
+        <v>336</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11338,7 +11338,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>160</v>
@@ -11368,7 +11368,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
@@ -11377,7 +11377,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11509,7 +11509,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11538,17 +11538,17 @@
         <v>23</v>
       </c>
       <c t="s" r="C329" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>20</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11602,17 +11602,17 @@
         <v>23</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11639,7 +11639,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>105</v>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11709,7 +11709,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>238</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11859,7 +11859,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11955,7 +11955,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>22</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12039,7 +12039,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12102,7 +12102,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>150</v>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12168,7 +12168,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>185</v>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12201,7 +12201,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>145</v>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12282,7 +12282,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>151</v>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12315,7 +12315,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>118</v>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12354,11 +12354,11 @@
         <v>145</v>
       </c>
       <c t="s" r="K355" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12613,7 +12613,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>272</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12697,7 +12697,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12805,7 +12805,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>182</v>
@@ -12829,13 +12829,13 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>17</v>
@@ -12844,7 +12844,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12871,7 +12871,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>43</v>
@@ -12895,13 +12895,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>17</v>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12937,7 +12937,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>175</v>
@@ -12961,13 +12961,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13021,7 +13021,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>106</v>
@@ -13042,7 +13042,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13090,7 +13090,7 @@
         <v>325</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13186,10 +13186,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13255,7 +13255,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13399,7 +13399,7 @@
         <v>206</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>67</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13480,7 +13480,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>234</v>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13546,10 +13546,10 @@
         <v>248</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13579,7 +13579,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>302</v>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14038,7 +14038,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>255</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14215,7 +14215,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>242</v>
@@ -14239,13 +14239,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>17</v>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14386,7 +14386,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14617,7 +14617,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14665,7 +14665,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14812,7 +14812,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14839,7 +14839,7 @@
         <v>115</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>274</v>
@@ -14863,13 +14863,13 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>115</v>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15022,7 +15022,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>275</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15085,7 +15085,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>218</v>
@@ -15109,13 +15109,13 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>17</v>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15169,7 +15169,7 @@
         <v>248</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>305</v>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15238,7 +15238,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -15364,10 +15364,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>195</v>
@@ -15388,13 +15388,13 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>20</v>
@@ -15403,7 +15403,7 @@
         <v>251</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -15445,7 +15445,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>59</v>
@@ -15469,13 +15469,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>17</v>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -15511,7 +15511,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>125</v>
@@ -15535,13 +15535,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>17</v>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
@@ -15583,7 +15583,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15609,14 +15609,14 @@
         <v>13</v>
       </c>
       <c r="B463" s="7">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c t="s" r="C463" s="7">
         <v>14</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -15625,13 +15625,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>304</v>
+        <v>112</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15642,29 +15642,29 @@
         <v>13</v>
       </c>
       <c r="B464" s="7">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c t="s" r="C464" s="7">
         <v>14</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -15793,7 +15793,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>154</v>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -15904,10 +15904,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H472" s="8">
+        <v>337</v>
+      </c>
+      <c t="s" r="I472" s="7">
         <v>336</v>
-      </c>
-      <c t="s" r="I472" s="7">
-        <v>386</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>306</v>
@@ -15934,7 +15934,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>20</v>
@@ -16153,7 +16153,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J480" s="7">
         <v>44</v>
@@ -16288,7 +16288,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16369,7 +16369,7 @@
         <v>304</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -16615,7 +16615,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -16759,7 +16759,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I500" s="7">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c t="s" r="J500" s="7">
         <v>36</v>
@@ -16939,7 +16939,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J506" s="7">
         <v>244</v>
@@ -16972,7 +16972,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I507" s="7">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c t="s" r="J507" s="7">
         <v>55</v>
@@ -17266,7 +17266,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I517" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="J517" s="7">
         <v>254</v>
@@ -17541,7 +17541,7 @@
         <v>413</v>
       </c>
       <c t="s" r="C528" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="L530" s="7"/>
       <c t="s" r="M530" s="7">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="531" ht="14.25" customHeight="1">
